--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0053.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0053.xlsx
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Brant à... Ta còn tưởng ngươi chẳng đến sớm thế này đâu.</t>
+          <t>Brant à... Tao còn tưởng mày chẳng đến sớm thế này đâu.</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Ngươi đã gặp đám thuộc hạ của ta rồi. Những linh hồn tội nghiệp ấy… Ta làm tất cả vì chúng, để cho chúng cuộc sống xứng đáng. Một cuộc sống… hạnh phúc, bình yên.</t>
+          <t>Mày đã gặp đám thuộc hạ của tao rồi. Những linh hồn tội nghiệp ấy… Tao làm tất cả vì chúng, để cho chúng cuộc sống xứng đáng. Một cuộc sống… hạnh phúc, bình yên.</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Aaaaa! Còn ngươi, ờ... ở lại đây bảo vệ sự nghiệp vĩ đại của chúng ta đi! Cho bọn nó thấy sức mạnh thật sự của Fool's Troupe. TẠM BIỆT!</t>
+          <t>Aaaaa! Còn mày, ờ... ở lại đây bảo vệ sự nghiệp vĩ đại của chúng ta đi! Cho bọn nó thấy sức mạnh thật sự của Fool's Troupe. TẠM BIỆT!</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Haha! Ta biết là sẽ có lối thoát mà.</t>
+          <t>Haha! Tao biết là sẽ có lối thoát mà.</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6489,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Nguyền rủa... *Cái này* mới là lời nguyền! Vàng của ta... vàng của ta đang tự di chuyển!</t>
+          <t>Nguyền rủa... *Cái này* mới là lời nguyền! Vàng của tao... vàng của tao đang tự di chuyển!</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Aldric chỉ cười khẩy, gọi đó là hành động ngu ngốc. Hắn nói: "Đồ ngốc! Với kho báu của Drake, ngươi có thể đè bẹp bất kỳ ai và bắt cả thế giới phải sống tốt hơn bằng nắm đấm của mình!"</t>
+          <t>Aldric chỉ cười khẩy, gọi đó là hành động ngu ngốc. Hắn nói: "Đồ ngốc! Với kho báu của Drake, mày có thể đè bẹp bất kỳ ai và bắt cả thế giới phải sống tốt hơn bằng nắm đấm của mình!"</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Thật lòng, lúc trao đổi, ta cũng không biết mình sẽ nhận được gì.</t>
+          <t>Thật lòng, lúc trao đổi, tao cũng không biết mình sẽ nhận được gì.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Mỗi lần có lệnh truy nã treo trên đầu, ta lại hợp tác với băng của mình. Bọn họ giao ta cho người ta lấy tiền thưởng, còn ta thì lo đường thoát thân.</t>
+          <t>Mỗi lần có lệnh truy nã treo trên đầu, tao lại hợp tác với băng của mình. Bọn họ giao tao cho người ta lấy tiền thưởng, còn tao thì lo đường thoát thân.</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Mỗi khi cuộc phiêu lưu lớn tiếp theo gọi tên, cứ tính ta vào. Ta đã sẵn sàng!</t>
+          <t>Mỗi khi cuộc phiêu lưu lớn tiếp theo gọi tên, cứ tính tao vào. Tao đã sẵn sàng!</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Ta đến đây!</t>
+          <t>Tao đến đây!</t>
         </is>
       </c>
     </row>
@@ -13316,7 +13316,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Xin chào, {PlayerName}.</t>
+          <t>Chào {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -13706,7 +13706,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Nếu {Male=anh ấy;Female=cô ấy} Nhà Học Giả có mặt ở đây, chắc tớ đã không lo lắng đến vậy. Mọi chuyện sẽ dễ dàng hơn nhiều.</t>
+          <t>Nếu {Male=himself;Female=herself} Nhà Học Giả có mặt ở đây, chắc tớ đã không lo lắng đến vậy. Mọi chuyện sẽ dễ dàng hơn nhiều.</t>
         </is>
       </c>
     </row>
@@ -25278,7 +25278,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Ừ thì, ta vẫn sẽ cố tìm nó. Luôn có cơ hội mà, phải không?</t>
+          <t>Ừ thì, tao vẫn sẽ cố tìm nó. Luôn có cơ hội mà, phải không?</t>
         </is>
       </c>
     </row>
@@ -26253,7 +26253,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Vì giờ cậu là Tân Rover rồi, chắc chắn sẽ không còn ai bị trục xuất nữa đâu.</t>
+          <t>Vì giờ cậu là Tân Vận Mệnh Giả rồi, chắc chắn sẽ không còn ai bị trục xuất nữa đâu.</t>
         </is>
       </c>
     </row>
@@ -29119,7 +29119,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Để tôi lo.</t>
+          <t>Để đó cho ta.</t>
         </is>
       </c>
     </row>
@@ -29643,7 +29643,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Cái mê cung sương mù này khiến ta có cảm giác quen quen.</t>
+          <t>Cái mê cung sương mù này khiến tao có cảm giác quen quen.</t>
         </is>
       </c>
     </row>
@@ -32895,7 +32895,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Ôi, cảm ơn cậu... Đây là bữa ăn ngon nhất của tôi kể từ khi lên con tàu đó.</t>
+          <t>Ôi, cảm ơn bạn... Đây là bữa ăn ngon nhất của tôi kể từ khi lên con tàu đó.</t>
         </is>
       </c>
     </row>
